--- a/document/TaskMan_一覧表示機能_詳細クラス図.xlsx
+++ b/document/TaskMan_一覧表示機能_詳細クラス図.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ADD9DA-BB9E-4EBD-BC21-1B095DC8263E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44D6671-ECF6-40CA-A040-F66E07D5D16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -406,6 +406,33 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -427,9 +454,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -471,30 +495,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -518,60 +518,49 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>60406</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>305083</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>124691</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{846D1338-E1FE-2B4A-48CD-7051CCEB5037}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41BC3A4-9445-5B36-C50C-9CB649B703AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="219075" y="866774"/>
-          <a:ext cx="8210550" cy="7147007"/>
+          <a:off x="0" y="1047751"/>
+          <a:ext cx="9134758" cy="6144490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -786,19 +775,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="21" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="21" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="22"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -810,564 +799,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="23" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="23" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="5">
+      <c r="G2" s="32"/>
+      <c r="H2" s="14">
         <v>46177</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="9"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="10"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="11"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="12"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="29"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="31"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="27"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="31"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="27"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="27"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="27"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="31"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="27"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="27"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="31"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="27"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="27"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="27"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="31"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="27"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="31"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="27"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="31"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="27"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="31"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="27"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="31"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="31"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="27"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="31"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="27"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="31"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="31"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="27"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="31"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="27"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="31"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="27"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="31"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="27"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="31"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="27"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="31"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="27"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="31"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="27"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="31"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="27"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="31"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="10"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="27"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="31"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="27"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="31"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="10"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="27"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="31"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="27"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="31"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="10"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="27"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="31"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="10"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="27"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="31"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="10"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="27"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="31"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="10"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="27"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="31"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="10"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="27"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="31"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="10"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="27"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="31"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="10"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="32"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="34"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
